--- a/www/download/IND.compensation.empe_ms.r.pc.rpA2.xlsx
+++ b/www/download/IND.compensation.empe_ms.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>0.37847368190924</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>0.378806594382501</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>0.379326311097916</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0.380031673104945</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>0.380924411145202</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>0.382009092927736</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>0.383293158770534</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>0.381499114359128</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>0.380542432698167</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>0.392477390240563</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404215425231224</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404215425231224</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404215425231224</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404215425231224</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404215425231224</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>0.671010166280092</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>0.680511013366372</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>0.686200441353039</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>0.685156538978708</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>0.656510514138975</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65.53</t>
+          <t>0.655278617902113</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>0.661846026462975</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>66.11</t>
+          <t>0.661078921494902</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>0.63577070785497</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>0.63137656510983</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>0.643327008916173</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>0.64238490261995</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>63.94</t>
+          <t>0.639442539353564</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>0.651407027183705</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>0.649049853514358</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>0.445526173294926</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>0.457877195974051</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467406095339612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>0.475852796445434</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>0.480561974817937</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>0.49979139344762</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>0.511218651781974</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>0.519639347364957</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>0.502523407533596</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>0.545194857547996</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>0.554528964233844</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>0.561598394579096</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>0.573414145424168</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>0.564980568882856</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>0.569376291647569</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>0.169808085044118</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>0.176824940679784</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>0.168692369777653</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.160217209274112</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>0.174665667557867</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>0.179910216418803</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>0.187035676667841</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>0.18621192661329</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>0.133184295915879</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>0.195344038586568</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197423507628787</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>0.207830894374601</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.199025936164546</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197474450575818</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>0.216775569682832</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>0.302847446399263</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>0.308080715976869</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>0.313313985554475</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318547255132081</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>0.323780524709687</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>0.329013794287293</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>0.334247063864899</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>0.339480333442505</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>0.347788509864734</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>35.61</t>
+          <t>0.356096686286962</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>0.36440486270919</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>0.370335501013448</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>0.376266139317706</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>0.382196777621964</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>0.388127415926222</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>0.777580178303824</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>0.773047863670747</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>0.764365399958455</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>76.01</t>
+          <t>0.76011374745345</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>0.765582903940644</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>76.32</t>
+          <t>0.763194950347046</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>0.756955280826279</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>0.753490805886111</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>75.36</t>
+          <t>0.753646248571463</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>0.749574489514505</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>74.58</t>
+          <t>0.745810508452688</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>0.735992500871819</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>73.28</t>
+          <t>0.732808213124645</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>0.738094910441187</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>0.725483562503862</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>0.443790668260678</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>0.452136418603582</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>0.460255196955978</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>0.4681321380586</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>47.58</t>
+          <t>0.475753011927834</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>0.483104273846828</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>0.490173109323406</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>0.496947473486285</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>0.485234087664569</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>0.472155254567998</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>0.458939788004176</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>0.44538179323064</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0.440040375197511</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>0.436009295706546</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>0.436009295706546</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>0.321293200762932</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>0.328626938735117</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>0.322348896331952</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>0.315242186789605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>0.337233876652075</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.342979664793355</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>0.349594082475155</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>0.348925892107897</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>0.338509157324964</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>0.365575717545096</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>0.379463226115965</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>0.387763044649832</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>0.383128728066806</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>0.395468700852395</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>0.399773244605587</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>0.766760438555195</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>0.766760438555195</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>0.766760438555195</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>0.766760438555195</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>0.764606255087522</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.12</t>
+          <t>0.761221530850925</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>0.759783404645724</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>0.758548259103415</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>0.755796073865582</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>0.753244363573396</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>0.754922311106197</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.92</t>
+          <t>0.749235944721564</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>0.745383539411571</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>0.742689920171966</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>0.730952614362941</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>0.59454138680484</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>0.595258406339624</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>0.594653617929654</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>0.584727948123357</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>0.588371699399295</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>0.583821059901513</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>0.578503908321464</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>56.95</t>
+          <t>0.569470000808505</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>55.05</t>
+          <t>0.550528974734686</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.560057982965693</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>54.99</t>
+          <t>0.549858319779674</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>0.55309471873137</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>0.557789083181953</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>0.555608619892097</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>0.54494562514477</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>0.550590716553441</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>0.553503630601798</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>0.553976662936635</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>0.553250491018004</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>0.554990553961462</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>55.47</t>
+          <t>0.554732294142613</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>0.553521750790115</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>0.552981915247363</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>0.521002579797404</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>0.516869446873403</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>0.497784424326814</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>0.501836405989754</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>0.466878590140647</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>0.466304492760894</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>0.450798377646792</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>0.161798090887162</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>0.171762080787493</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>0.179831615394149</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>0.186337128429743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>0.190972227950267</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>0.195922528300967</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>0.195522472732045</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>0.19724866341156</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>0.183891902154676</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>0.211860667773598</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>0.226658017483415</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.233821687109926</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>0.233229578689497</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>0.237976856018813</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>0.234416934733873</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>0.495833562839275</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>0.505335916986218</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>0.507567636861314</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>0.510313637691528</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>0.530444633195852</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>0.529587032593355</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>53.46</t>
+          <t>0.534578002160968</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>0.533321226370326</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>0.532121704033019</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>0.525422647058035</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>0.511536690506456</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>50.66</t>
+          <t>0.506614254744889</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>0.530096368124594</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>0.527774495260558</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>52.36</t>
+          <t>0.523574013489296</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>0.402729758764687</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>0.408709118495148</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>0.414861778032466</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418897551821378</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>0.419807628286951</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>0.426340817820327</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>0.432089115527316</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>0.435300420804858</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>0.439944509231172</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>0.442742323919603</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>0.442416584481061</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>0.444235964690608</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>0.430430710493054</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.42698941120088</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0.422997689638566</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>0.413160058376902</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>0.408308998377964</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>0.416854454368195</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>0.417823808883355</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>0.422771084810526</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0.423025368000451</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0.42603043269786</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>0.434453621079153</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.420193041419233</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>0.442463877183327</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>0.440757438924035</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>0.434024045809127</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>0.438329512209324</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0.439977971085183</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>42.37</t>
+          <t>0.423741093157066</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>0.415303017138807</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>0.416234283839518</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435409014035973</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>0.433675026228324</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.432040079440748</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>0.420134869664512</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>0.412186031559375</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>0.413691429736799</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>0.431608389644541</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>0.446891177916702</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>0.444916896543453</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0.442551596604485</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>0.422380180206385</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>0.417104646342857</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.427590105531019</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>0.290971559363126</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>0.306187083248416</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>0.328277512911752</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0.351647277091884</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>0.385448066759675</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.399968076680631</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>0.39776995231038</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>0.407244687140934</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>0.395545170131403</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>0.433181801876958</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>0.440875469224604</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>0.399134350888723</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>0.401697600956369</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>0.404309922144322</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>0.400615216883796</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>0.613892332189813</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>0.613892332189813</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>0.613892332189813</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>0.613892332189813</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>0.615653264914631</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>0.606726649721676</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>0.611500965395145</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>0.615664483182112</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>58.22</t>
+          <t>0.582153996933471</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>0.596512468348034</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>0.592116281423768</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>0.594573862935085</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>0.593801367594568</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>0.579629299768395</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>0.585373655534772</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>0.295696859929278</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>0.295696859929278</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>0.3114356161181</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>0.312318424954401</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>0.305843787252101</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>0.307091871869717</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>0.306444040432225</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>0.322153545857454</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0.330008298570068</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>33.79</t>
+          <t>0.337863051282682</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>0.299021406845584</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.279600584627035</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>0.295540888760317</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>0.295540888760317</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>0.295540888760317</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>0.426572864616802</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.434971395509284</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>0.443369926401766</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>0.451768457294249</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>0.460166988186731</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>0.444450156426241</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>0.428733324665752</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.413016492905263</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>0.397299661144773</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381582829384284</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381582829384284</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381582829384284</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381582829384284</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381582829384284</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381582829384284</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>0.420987678638385</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>0.437758976405333</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>0.449934012124202</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>0.448791732503489</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>0.446990165169487</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>0.443127372849649</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>0.434154610173299</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.429782298577874</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>0.421636914152267</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>0.407857989703823</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>0.38679683229293</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>0.378179481889638</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>0.370278519530993</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>0.362968876895351</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>0.358388550232721</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>0.330346728312496</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>0.34945440899313</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>0.369075878158331</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>0.389581381411308</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>0.396906296214269</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>0.418701443239057</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>0.411514557796667</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>0.422333833744622</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>0.39435686951909</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.463301239446308</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>0.468235395421219</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>0.476813202042057</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>0.479029026662959</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>0.462192916504095</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>0.473675289854856</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>0.582530546331134</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>0.586060041193847</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>0.590377919030962</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>59.19</t>
+          <t>0.591940917362233</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>0.595380718738523</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>0.598079257768512</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>0.598630257895856</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>59.19</t>
+          <t>0.591938496678375</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>0.598516075120748</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>59.66</t>
+          <t>0.596621977659668</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.595962081413037</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.595962081413037</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.595962081413037</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.595962081413037</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.595962081413037</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>0.436166942521148</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>0.430448852721004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>0.435615610218396</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>0.42882899269932</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0.419954649183771</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.427606828039</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>0.418059720586339</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>0.403877621841788</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>0.403828393058087</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>0.410036099509903</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>0.395258537696225</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>0.395258537696225</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>0.395258537696225</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>0.395258537696225</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>0.395258537696225</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>0.551165908038753</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.56012188209631</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>56.27</t>
+          <t>0.562656144083645</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>56.54</t>
+          <t>0.565446055716564</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>0.58347578064208</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>0.584354733603416</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>0.589745862974171</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>0.587979910136802</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>0.579241250905231</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>0.571140274425083</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>0.562470444100666</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>0.562069271680628</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>0.545168024157812</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>0.543979820692733</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>0.532984201290888</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>0.328135758070723</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>0.340693467003098</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>0.389295235470385</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>0.434256474850671</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>0.475170925537629</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.463349475360647</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>0.455797139460949</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>0.455185052679172</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>0.432520831947049</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>0.424571573023134</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>0.417254082267022</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435439149657932</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>0.410471791914278</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.420186507374171</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>0.41861620311448</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>0.552308389577755</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>56.09</t>
+          <t>0.56085972469758</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.560053731319587</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>0.558693728344203</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>0.579239365217289</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>0.581020229331219</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>0.587151450348968</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>0.587498722179865</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>0.604007867943318</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>0.59501943934149</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>0.60436958624526</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>0.597569119132053</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>57.08</t>
+          <t>0.570767725225988</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>0.519722552787632</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>52.95</t>
+          <t>0.529510388783344</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>0.501790530443466</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>0.50831822335499</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>52.22</t>
+          <t>0.522194384124724</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>0.525544138503226</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>0.525459760371842</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>0.525374221911579</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>0.539308999910502</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>0.542902796758459</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>55.08</t>
+          <t>0.550798441737517</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>0.561289759096373</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>0.570412002924493</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>0.584321115045995</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>0.587261079617403</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>59.39</t>
+          <t>0.593873331052796</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>59.39</t>
+          <t>0.593873331052796</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>0.169808085044118</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>0.176824940679784</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>0.168692369777653</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.160217209274112</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>0.174665667557867</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>0.179910216418803</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>0.187035676667841</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>0.18621192661329</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>0.133184295915879</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>0.195344038586568</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197423507628787</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>0.207830894374601</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.199025936164546</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197474450575818</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>0.216775569682832</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>0.472347731883114</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>0.47653385884818</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>0.465950798332348</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>0.466940112032318</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>0.456406384073613</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>0.438976928050973</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>0.443243792582819</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>0.452809302409808</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>0.410788258385951</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>0.426703245660015</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>0.426587881750408</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>42.73</t>
+          <t>0.427302669921315</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>0.441127002744028</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>0.417658099060937</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>0.414835106175788</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728913401470213</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728913401470213</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728913401470213</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728913401470213</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728913401470213</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728913401470213</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>71.37</t>
+          <t>0.713749162074466</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>0.704022519621681</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>0.682689167535268</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>0.67044334674335</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>66.25</t>
+          <t>0.662467146601343</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>0.656010408643502</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>0.646989663617845</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>0.649286049704992</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>0.631515982679652</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>0.169808085044118</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>0.176824940679784</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>0.168692369777653</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.160217209274112</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>0.174665667557867</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>0.179910216418803</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>0.187035676667841</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>0.18621192661329</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>0.133184295915879</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>0.195344038586568</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197423507628787</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>0.207830894374601</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.199025936164546</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197474450575818</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>0.216775569682832</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>0.169808085044118</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>0.176824940679784</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>0.168692369777653</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.160217209274112</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>0.174665667557867</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>0.179910216418803</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>0.187035676667841</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>0.18621192661329</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>0.133184295915879</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>0.195344038586568</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197423507628787</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>0.207830894374601</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.199025936164546</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197474450575818</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>0.216775569682832</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>0.723675629110238</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>0.723675629110238</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>0.723675629110238</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>0.723675629110238</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>72.08</t>
+          <t>0.720836831233209</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>0.717701641385584</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>71.57</t>
+          <t>0.715688374619273</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>0.713068185136395</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>0.713219656479643</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>71.52</t>
+          <t>0.715184419634513</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>0.712203752107516</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>0.712203752107516</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>0.712203752107516</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>0.712203752107516</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>0.712203752107516</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>0.758796601193078</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>0.758796601193078</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>0.758796601193078</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>0.758796601193078</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0.773284567686399</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>0.776372324109149</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>0.778684350268195</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79.12</t>
+          <t>0.791171388899219</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>0.773020074994206</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>77.11</t>
+          <t>0.771119572719882</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>75.24</t>
+          <t>0.752394254379362</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>0.742645730092074</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>0.752520864796886</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>0.746381587509367</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>0.741808409964212</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>0.624435919070539</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>0.624435919070539</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>0.624435919070539</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>0.624435919070539</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>0.628636805898128</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>0.603415954512167</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>63.84</t>
+          <t>0.63837916359736</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>62.09</t>
+          <t>0.620910986397626</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>60.03</t>
+          <t>0.600341285626231</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>59.41</t>
+          <t>0.594092410633173</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>0.590468665356388</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>0.592062285047216</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>0.58441641414411</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0.58000538446106</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>0.566979901880087</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>0.568263560293997</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>0.574674634470877</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>0.580260119671008</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>0.586000513061219</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>0.574163857675759</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>0.582930939050782</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>0.583532617697635</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>0.584072145887833</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>0.583415741425941</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>0.585317212081492</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>0.581267224553589</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>0.574570886085595</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>0.570379798923343</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>56.12</t>
+          <t>0.561167767493832</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>0.530134638009854</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>0.224562015410273</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>0.233966072771193</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>0.231402199416765</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>0.244512742989034</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>0.241659550790121</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>0.249225344328062</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>0.254082731610233</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>0.257985594241123</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>0.264082328164442</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>0.267681917957441</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>0.274590947512387</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>0.277608235050942</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>0.286027236388928</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>0.290834914191311</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>0.295114194482208</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>0.308343832456194</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>0.311591700769992</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>0.314870815048877</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>0.31818036630264</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>0.321519643434556</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>0.324888026905767</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>0.328284983091023</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>0.331710059251875</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>0.331430527503408</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>0.33119171473992</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>0.32956276626521</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>0.32336906100886</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>0.329465738342722</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>0.325787181809133</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>0.332430771654221</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>0.584390359486787</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>59.03</t>
+          <t>0.590349649645511</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>58.28</t>
+          <t>0.582830657193358</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>0.583688997296989</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>0.582617935738407</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>0.573386304427815</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>0.566839573924319</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>56.35</t>
+          <t>0.563500494379218</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>0.567575384021138</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>0.557947784553062</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557538159938588</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>54.94</t>
+          <t>0.549410554976046</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>0.558717571172456</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>0.55023438139401</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>54.94</t>
+          <t>0.549429508172603</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>0.453619150842876</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>0.458991502302581</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463130386661843</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>0.465589634981445</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>0.471018569897122</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>0.471636483388593</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>0.473224520750676</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>0.47349384372661</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>0.460707877633889</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>0.472300993256089</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>0.470266756125835</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>0.469502423185547</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>0.466965109699573</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>0.464136590079048</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.463349681517467</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>0.453619150842876</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>0.458991502302581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463130386661843</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>0.465589634981445</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>0.471018569897122</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>0.471636483388593</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>0.473224520750676</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>0.47349384372661</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>0.460707877633889</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>0.472300993256089</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>0.470266756125835</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>0.469502423185547</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>0.466965109699573</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>0.464136590079048</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.463349681517467</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>compensation.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
